--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_1.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_1.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0086144378372235</v>
+        <v>0.0008192588077755108</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008415597809022419</v>
+        <v>0.008408531073609142</v>
       </c>
       <c r="C2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>4794131</v>
+        <v>5017027</v>
       </c>
       <c r="L2" t="n">
-        <v>2954590</v>
+        <v>3241692</v>
       </c>
       <c r="M2" t="n">
-        <v>792544</v>
+        <v>916193</v>
       </c>
       <c r="N2" t="n">
-        <v>47659</v>
+        <v>66949</v>
       </c>
       <c r="O2" t="n">
-        <v>458992</v>
+        <v>508074</v>
       </c>
       <c r="P2" t="n">
-        <v>178382</v>
+        <v>190968</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999977946281433</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9554627537727356</v>
+        <v>0.9974434971809387</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9039219617843628</v>
+        <v>0.9880505204200745</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8496689200401306</v>
+        <v>0.9806711673736572</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7019515633583069</v>
+        <v>0.9843848943710327</v>
       </c>
       <c r="V2" t="n">
-        <v>0.896503746509552</v>
+        <v>0.9916889667510986</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9328089952468872</v>
+        <v>0.9986246824264526</v>
       </c>
       <c r="X2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>6296277</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>4808782</v>
+        <v>4825783</v>
       </c>
       <c r="AG2" t="n">
-        <v>2955373</v>
+        <v>2962430</v>
       </c>
       <c r="AH2" t="n">
-        <v>798205</v>
+        <v>798977</v>
       </c>
       <c r="AI2" t="n">
-        <v>58883</v>
+        <v>58950</v>
       </c>
       <c r="AJ2" t="n">
-        <v>458685</v>
+        <v>458776</v>
       </c>
       <c r="AK2" t="n">
         <v>180009</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566851854324341</v>
+        <v>0.9567543864250183</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112403392791748</v>
+        <v>0.9111810326576233</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8584150671958923</v>
+        <v>0.8583831191062927</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6629027724266052</v>
+        <v>0.6629480123519897</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9021613597869873</v>
+        <v>0.9021487236022949</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,88 +786,88 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00198335418273572</v>
+        <v>0.0001598347447050582</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002018522500489981</v>
+        <v>0.002016202349440813</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4794131</v>
+        <v>5017027</v>
       </c>
       <c r="E3" t="n">
-        <v>215200</v>
+        <v>21857</v>
       </c>
       <c r="F3" t="n">
-        <v>10062</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>1577</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9990109</v>
+        <v>10016608</v>
       </c>
       <c r="K3" t="n">
-        <v>11041795</v>
+        <v>11277843</v>
       </c>
       <c r="L3" t="n">
-        <v>12724593</v>
+        <v>13035078</v>
       </c>
       <c r="M3" t="n">
-        <v>15215786</v>
+        <v>15380188</v>
       </c>
       <c r="N3" t="n">
-        <v>16177265</v>
+        <v>16239533</v>
       </c>
       <c r="O3" t="n">
-        <v>15724739</v>
+        <v>15816557</v>
       </c>
       <c r="P3" t="n">
-        <v>16080288</v>
+        <v>16136074</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9547902941703796</v>
+        <v>0.9956595897674561</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9097307920455933</v>
+        <v>0.9958145618438721</v>
       </c>
       <c r="T3" t="n">
-        <v>0.851840615272522</v>
+        <v>0.9837215542793274</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5361027717590332</v>
+        <v>0.7521936893463135</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9023321270942688</v>
+        <v>0.998602569103241</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9230012893676758</v>
+        <v>0.9881249666213989</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4808782</v>
+        <v>4825783</v>
       </c>
       <c r="Z3" t="n">
-        <v>197044</v>
+        <v>197772</v>
       </c>
       <c r="AA3" t="n">
-        <v>8483</v>
+        <v>8501</v>
       </c>
       <c r="AB3" t="n">
-        <v>6751</v>
+        <v>6767</v>
       </c>
       <c r="AC3" t="n">
         <v>45</v>
@@ -876,43 +876,43 @@
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>9990123</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>11047543</v>
+        <v>11072575</v>
       </c>
       <c r="AG3" t="n">
-        <v>12750768</v>
+        <v>12785515</v>
       </c>
       <c r="AH3" t="n">
-        <v>15224356</v>
+        <v>15266430</v>
       </c>
       <c r="AI3" t="n">
-        <v>16167558</v>
+        <v>16210624</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15727983</v>
+        <v>15771054</v>
       </c>
       <c r="AK3" t="n">
-        <v>16079883</v>
+        <v>16123083</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577081799507141</v>
+        <v>0.9577060341835022</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099718928337097</v>
+        <v>0.9100281000137329</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8579251766204834</v>
+        <v>0.8578660488128662</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6623584032058716</v>
+        <v>0.6623223423957825</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901728630065918</v>
+        <v>0.9017089605331421</v>
       </c>
       <c r="AR3" t="n">
         <v>0.931419849395752</v>
@@ -920,88 +920,88 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03240545785072844</v>
+        <v>0.00702487587950196</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03185503593778934</v>
+        <v>0.03183346841779339</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>209164</v>
+        <v>12760</v>
       </c>
       <c r="E4" t="n">
-        <v>2954590</v>
+        <v>3241692</v>
       </c>
       <c r="F4" t="n">
-        <v>80935</v>
+        <v>858</v>
       </c>
       <c r="G4" t="n">
-        <v>1825</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1201</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>223470</v>
+        <v>12859</v>
       </c>
       <c r="L4" t="n">
-        <v>314044</v>
+        <v>39205</v>
       </c>
       <c r="M4" t="n">
-        <v>140224</v>
+        <v>18058</v>
       </c>
       <c r="N4" t="n">
-        <v>20236</v>
+        <v>1062</v>
       </c>
       <c r="O4" t="n">
-        <v>52988</v>
+        <v>4258</v>
       </c>
       <c r="P4" t="n">
-        <v>12849</v>
+        <v>263</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999988675117493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9551264047622681</v>
+        <v>0.9965507388114929</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9068170785903931</v>
+        <v>0.9919173717498779</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8507533669471741</v>
+        <v>0.9821940064430237</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6079187393188477</v>
+        <v>0.8527666330337524</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8994084596633911</v>
+        <v>0.9951337575912476</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9278792142868042</v>
+        <v>0.9933471083641052</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>203271</v>
+        <v>203648</v>
       </c>
       <c r="Z4" t="n">
-        <v>2955373</v>
+        <v>2962430</v>
       </c>
       <c r="AA4" t="n">
-        <v>82450</v>
+        <v>82563</v>
       </c>
       <c r="AB4" t="n">
-        <v>5465</v>
+        <v>5472</v>
       </c>
       <c r="AC4" t="n">
         <v>1136</v>
@@ -1013,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>217722</v>
+        <v>218127</v>
       </c>
       <c r="AG4" t="n">
-        <v>287869</v>
+        <v>288768</v>
       </c>
       <c r="AH4" t="n">
-        <v>131654</v>
+        <v>131816</v>
       </c>
       <c r="AI4" t="n">
-        <v>29943</v>
+        <v>29971</v>
       </c>
       <c r="AJ4" t="n">
-        <v>49744</v>
+        <v>49761</v>
       </c>
       <c r="AK4" t="n">
         <v>13254</v>
@@ -1034,19 +1034,19 @@
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571964144706726</v>
+        <v>0.9572299718856812</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106056094169617</v>
+        <v>0.9106041789054871</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8581700325012207</v>
+        <v>0.8581244349479675</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6626304984092712</v>
+        <v>0.6626349687576294</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9019449949264526</v>
+        <v>0.9019287824630737</v>
       </c>
       <c r="AR4" t="n">
         <v>0.931419849395752</v>
@@ -1059,82 +1059,82 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8073</v>
+        <v>83</v>
       </c>
       <c r="E5" t="n">
-        <v>90866</v>
+        <v>14538</v>
       </c>
       <c r="F5" t="n">
-        <v>792544</v>
+        <v>916193</v>
       </c>
       <c r="G5" t="n">
-        <v>9086</v>
+        <v>539</v>
       </c>
       <c r="H5" t="n">
-        <v>29253</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>227004</v>
+        <v>21871</v>
       </c>
       <c r="L5" t="n">
-        <v>293173</v>
+        <v>13625</v>
       </c>
       <c r="M5" t="n">
-        <v>137846</v>
+        <v>15161</v>
       </c>
       <c r="N5" t="n">
-        <v>41240</v>
+        <v>22056</v>
       </c>
       <c r="O5" t="n">
-        <v>49681</v>
+        <v>711</v>
       </c>
       <c r="P5" t="n">
-        <v>14881</v>
+        <v>2295</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999991655349731</v>
       </c>
       <c r="R5" t="n">
-        <v>0.97234046459198</v>
+        <v>0.9978731870651245</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9627163410186768</v>
+        <v>0.9967647790908813</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9829262495040894</v>
+        <v>0.9979656934738159</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9962252974510193</v>
+        <v>0.9985842704772949</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9936960339546204</v>
+        <v>0.9996957182884216</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9982973337173462</v>
+        <v>0.9998433589935303</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>7974</v>
+        <v>7991</v>
       </c>
       <c r="Z5" t="n">
-        <v>84616</v>
+        <v>84775</v>
       </c>
       <c r="AA5" t="n">
-        <v>798205</v>
+        <v>798977</v>
       </c>
       <c r="AB5" t="n">
-        <v>9906</v>
+        <v>9911</v>
       </c>
       <c r="AC5" t="n">
-        <v>29056</v>
+        <v>29067</v>
       </c>
       <c r="AD5" t="n">
         <v>633</v>
@@ -1143,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>212353</v>
+        <v>213115</v>
       </c>
       <c r="AG5" t="n">
-        <v>292390</v>
+        <v>292887</v>
       </c>
       <c r="AH5" t="n">
-        <v>132185</v>
+        <v>132377</v>
       </c>
       <c r="AI5" t="n">
-        <v>30016</v>
+        <v>30055</v>
       </c>
       <c r="AJ5" t="n">
-        <v>49988</v>
+        <v>50009</v>
       </c>
       <c r="AK5" t="n">
         <v>13254</v>
@@ -1164,47 +1164,47 @@
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97359299659729</v>
+        <v>0.9735913872718811</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643715620040894</v>
+        <v>0.9643803238868713</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838000535964966</v>
+        <v>0.9838212132453918</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963184595108032</v>
+        <v>0.9963241219520569</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938763380050659</v>
+        <v>0.9938902258872986</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983723759651184</v>
+        <v>0.9983766674995422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6192</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>7082</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="n">
-        <v>19396</v>
+        <v>17185</v>
       </c>
       <c r="G6" t="n">
-        <v>47659</v>
+        <v>66949</v>
       </c>
       <c r="H6" t="n">
-        <v>8137</v>
+        <v>1995</v>
       </c>
       <c r="I6" t="n">
-        <v>429</v>
+        <v>47</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>6422</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>5319</v>
+        <v>5328</v>
       </c>
       <c r="AA6" t="n">
-        <v>10837</v>
+        <v>10850</v>
       </c>
       <c r="AB6" t="n">
-        <v>58883</v>
+        <v>58950</v>
       </c>
       <c r="AC6" t="n">
-        <v>6957</v>
+        <v>6963</v>
       </c>
       <c r="AD6" t="n">
         <v>481</v>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>29515</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>7551</v>
+        <v>493</v>
       </c>
       <c r="H7" t="n">
-        <v>458992</v>
+        <v>508074</v>
       </c>
       <c r="I7" t="n">
-        <v>11788</v>
+        <v>216</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1301,16 +1301,16 @@
         <v>27</v>
       </c>
       <c r="Z7" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>29554</v>
+        <v>29572</v>
       </c>
       <c r="AB7" t="n">
         <v>7556</v>
       </c>
       <c r="AC7" t="n">
-        <v>458685</v>
+        <v>458776</v>
       </c>
       <c r="AD7" t="n">
         <v>12042</v>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>14250</v>
+        <v>2262</v>
       </c>
       <c r="I8" t="n">
-        <v>178382</v>
+        <v>190968</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
